--- a/tests/eindhoven-500/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_conc_laag.xlsx
+++ b/tests/eindhoven-500/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_conc_laag.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Zone</t>
   </si>
@@ -28,7 +28,10 @@
     <t>OV</t>
   </si>
   <si>
-    <t>Auto-FietsOV_Fiets</t>
+    <t>Auto-Fiets</t>
+  </si>
+  <si>
+    <t>OV_Fiets</t>
   </si>
   <si>
     <t>Auto_OV</t>
@@ -391,6 +394,9 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2">

--- a/tests/eindhoven-500/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_conc_laag.xlsx
+++ b/tests/eindhoven-500/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_conc_laag.xlsx
@@ -978,7 +978,7 @@
         <v>0.9123563506511021</v>
       </c>
       <c r="C24">
-        <v>0.9762240648583298</v>
+        <v>0.9762240648583299</v>
       </c>
       <c r="D24">
         <v>0.7075007333880664</v>
@@ -1004,7 +1004,7 @@
         <v>0.9123563506511021</v>
       </c>
       <c r="C25">
-        <v>0.9762240648583299</v>
+        <v>0.97622406485833</v>
       </c>
       <c r="D25">
         <v>0.7075007333880665</v>
@@ -1030,7 +1030,7 @@
         <v>0.9123563506511021</v>
       </c>
       <c r="C26">
-        <v>0.9762240648583298</v>
+        <v>0.97622406485833</v>
       </c>
       <c r="D26">
         <v>0.7075007333880665</v>
@@ -7114,7 +7114,7 @@
         <v>0.59765982667205</v>
       </c>
       <c r="C260">
-        <v>0.5237220232685109</v>
+        <v>0.523722023268511</v>
       </c>
       <c r="D260">
         <v>0.9470082452668418</v>
@@ -9885,7 +9885,7 @@
         <v>0.9371830793744169</v>
       </c>
       <c r="H366">
-        <v>0.9538731324761341</v>
+        <v>0.953873132476134</v>
       </c>
     </row>
     <row r="367" spans="1:8">
@@ -9911,7 +9911,7 @@
         <v>0.9371830793744169</v>
       </c>
       <c r="H367">
-        <v>0.9538731324761341</v>
+        <v>0.953873132476134</v>
       </c>
     </row>
     <row r="368" spans="1:8">
@@ -9963,7 +9963,7 @@
         <v>0.9371830793744169</v>
       </c>
       <c r="H369">
-        <v>0.9538731324761341</v>
+        <v>0.953873132476134</v>
       </c>
     </row>
     <row r="370" spans="1:8">
@@ -11098,7 +11098,7 @@
         <v>0.5377315819055168</v>
       </c>
       <c r="E413">
-        <v>0.9001951740026319</v>
+        <v>0.9001951740026317</v>
       </c>
       <c r="F413">
         <v>0.7636947417137482</v>
@@ -11315,7 +11315,7 @@
         <v>0.6388985948302675</v>
       </c>
       <c r="H421">
-        <v>0.6413201388771879</v>
+        <v>0.641320138877188</v>
       </c>
     </row>
     <row r="422" spans="1:8">
